--- a/Result/profitability/2032.xlsx
+++ b/Result/profitability/2032.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>0.20375</v>
+        <v>0.26875</v>
       </c>
       <c r="N2" t="n">
-        <v>4.623749999999999</v>
+        <v>5.817500000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1625</v>
+        <v>0.2125</v>
       </c>
       <c r="N3" t="n">
-        <v>4.76625</v>
+        <v>5.73</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.83</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04250000000000001</v>
+        <v>0.08500000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>3.444999999999999</v>
+        <v>4.251250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.88</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09125</v>
+        <v>-0.01624999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3150000000000004</v>
+        <v>1.8625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.105</v>
+        <v>-0.06999999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2337500000000003</v>
+        <v>0.7850000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1025</v>
+        <v>-0.05999999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2825000000000003</v>
+        <v>0.9250000000000003</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08499999999999996</v>
+        <v>-0.07999999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8400000000000003</v>
+        <v>0.7550000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.13625</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3237499999999998</v>
+        <v>-0.32375</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.14625</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1425000000000002</v>
+        <v>0.1425</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>0.21</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.07999999999999997</v>
+        <v>-0.07999999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5075000000000003</v>
+        <v>0.5075000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>882</v>
+      </c>
+      <c r="D75" t="n">
+        <v>783</v>
+      </c>
+      <c r="E75" t="n">
+        <v>99</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>66</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>82</v>
+      </c>
+      <c r="K75" t="n">
+        <v>70</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.08163265306122458</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6799999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05714285714285716</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-8.571428571428571</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-10.67241379310345</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
